--- a/2025-2026/Data/Data_Dictionary.xlsx
+++ b/2025-2026/Data/Data_Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\Documents\NHL-Stats\2025-2026\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6EE82F5-FB48-4E6F-BF79-A041E15B7F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF726EEA-0D18-4160-8039-8AE1491954D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{63DB0C7C-412E-4A18-A7BF-880A50C6E4C7}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{63DB0C7C-412E-4A18-A7BF-880A50C6E4C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="104">
   <si>
     <t>Variable</t>
   </si>
@@ -231,6 +231,126 @@
   </si>
   <si>
     <t>game_story_data</t>
+  </si>
+  <si>
+    <t>period</t>
+  </si>
+  <si>
+    <t>event_id</t>
+  </si>
+  <si>
+    <t>time_in_period</t>
+  </si>
+  <si>
+    <t>time_remaining</t>
+  </si>
+  <si>
+    <t>situation_code</t>
+  </si>
+  <si>
+    <t>home_def_code</t>
+  </si>
+  <si>
+    <t>type_code</t>
+  </si>
+  <si>
+    <t>event_name</t>
+  </si>
+  <si>
+    <t>event_owner_team_id</t>
+  </si>
+  <si>
+    <t>zone_code</t>
+  </si>
+  <si>
+    <t>x_coord</t>
+  </si>
+  <si>
+    <t>y_coord</t>
+  </si>
+  <si>
+    <t>penl_code</t>
+  </si>
+  <si>
+    <t>penl_type</t>
+  </si>
+  <si>
+    <t>penl_len</t>
+  </si>
+  <si>
+    <t>drawn_by_player_id</t>
+  </si>
+  <si>
+    <t>commit_player_id</t>
+  </si>
+  <si>
+    <t>penalties</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the period that the event occurred </t>
+  </si>
+  <si>
+    <t>id number for the event</t>
+  </si>
+  <si>
+    <t xml:space="preserve">time remaining in the period when the event occurred </t>
+  </si>
+  <si>
+    <t xml:space="preserve">time elapsed in the period when the event occurred </t>
+  </si>
+  <si>
+    <t>4-digit code representing the players on the ice at the time of the event: away goalie-away skaters-home skaters- home goalie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The side of the ice the home team is on, which zone they're defending </t>
+  </si>
+  <si>
+    <t>numerical code indicating the event</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name of the event </t>
+  </si>
+  <si>
+    <t>zone the event occurred in. N=neutral, O=offensive, D=defensive</t>
+  </si>
+  <si>
+    <t>x-coordinate of the event</t>
+  </si>
+  <si>
+    <t xml:space="preserve">y coordinate of the event </t>
+  </si>
+  <si>
+    <t xml:space="preserve">name of the penalty that was called </t>
+  </si>
+  <si>
+    <t>the penalty type that was called: BEN=bench minor , GAM=game misconduct, MAJ=major, MAT=match penalty, MIN = minor, MIS=misconduct, PS=penalty shot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penalty length in minutes </t>
+  </si>
+  <si>
+    <t>id of the player who drew the penalty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id of the player who committed the penalty </t>
+  </si>
+  <si>
+    <t>l_player_id</t>
+  </si>
+  <si>
+    <t>w_player_id</t>
+  </si>
+  <si>
+    <t>faceoffs</t>
+  </si>
+  <si>
+    <t>team id code for the player who is responsible for the event</t>
+  </si>
+  <si>
+    <t>id of the player who lost the faceoff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id of the player who won the faceoff </t>
   </si>
 </sst>
 </file>
@@ -611,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94ACE342-EFD3-426B-82E7-62E8481985EA}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
@@ -960,6 +1080,369 @@
         <v>61</v>
       </c>
     </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>74</v>
+      </c>
+      <c r="B43" t="s">
+        <v>81</v>
+      </c>
+      <c r="C43" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" t="s">
+        <v>81</v>
+      </c>
+      <c r="C44" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>76</v>
+      </c>
+      <c r="B45" t="s">
+        <v>81</v>
+      </c>
+      <c r="C45" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>77</v>
+      </c>
+      <c r="B46" t="s">
+        <v>81</v>
+      </c>
+      <c r="C46" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" t="s">
+        <v>81</v>
+      </c>
+      <c r="C48" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" t="s">
+        <v>81</v>
+      </c>
+      <c r="C49" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52" t="s">
+        <v>100</v>
+      </c>
+      <c r="C52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" t="s">
+        <v>100</v>
+      </c>
+      <c r="C53" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>68</v>
+      </c>
+      <c r="B55" t="s">
+        <v>100</v>
+      </c>
+      <c r="C55" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56" t="s">
+        <v>100</v>
+      </c>
+      <c r="C56" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>70</v>
+      </c>
+      <c r="B57" t="s">
+        <v>100</v>
+      </c>
+      <c r="C57" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>71</v>
+      </c>
+      <c r="B58" t="s">
+        <v>100</v>
+      </c>
+      <c r="C58" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>72</v>
+      </c>
+      <c r="B59" t="s">
+        <v>100</v>
+      </c>
+      <c r="C59" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>73</v>
+      </c>
+      <c r="B60" t="s">
+        <v>100</v>
+      </c>
+      <c r="C60" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>74</v>
+      </c>
+      <c r="B61" t="s">
+        <v>100</v>
+      </c>
+      <c r="C61" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+      <c r="B62" t="s">
+        <v>100</v>
+      </c>
+      <c r="C62" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>98</v>
+      </c>
+      <c r="B63" t="s">
+        <v>100</v>
+      </c>
+      <c r="C63" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64" t="s">
+        <v>100</v>
+      </c>
+      <c r="C64" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025-2026/Data/Data_Dictionary.xlsx
+++ b/2025-2026/Data/Data_Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\Documents\NHL-Stats\2025-2026\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF726EEA-0D18-4160-8039-8AE1491954D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3554E4-538B-4B9E-A20C-3D2040C64C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{63DB0C7C-412E-4A18-A7BF-880A50C6E4C7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{63DB0C7C-412E-4A18-A7BF-880A50C6E4C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="160">
   <si>
     <t>Variable</t>
   </si>
@@ -351,6 +351,174 @@
   </si>
   <si>
     <t xml:space="preserve">id of the player who won the faceoff </t>
+  </si>
+  <si>
+    <t>shot_type</t>
+  </si>
+  <si>
+    <t>shoot_player_id</t>
+  </si>
+  <si>
+    <t>goalie_in_id</t>
+  </si>
+  <si>
+    <t>away_sog</t>
+  </si>
+  <si>
+    <t>home_sog</t>
+  </si>
+  <si>
+    <t>miss_reason</t>
+  </si>
+  <si>
+    <t>block_player_id</t>
+  </si>
+  <si>
+    <t>block_reason</t>
+  </si>
+  <si>
+    <t>all_shots</t>
+  </si>
+  <si>
+    <t>blocked_shots</t>
+  </si>
+  <si>
+    <t>id of the player who shot the puck</t>
+  </si>
+  <si>
+    <t>id of the player who blocked the shot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type of block: blocked, teammate blocked, other block </t>
+  </si>
+  <si>
+    <t>missed_shots</t>
+  </si>
+  <si>
+    <t>Type of shot: backhand, bat, between-legs, cradle, deflected, poke, slap, snap, tip-in, wrap-around, wrist</t>
+  </si>
+  <si>
+    <t>reason for the miss attempt: above-crossbar, failed-bank-attempt, high-and-wide-left, high-and-wide-right, hit-crossbar, hit-left-post, hit-right-post, short, wide-left, wide-right</t>
+  </si>
+  <si>
+    <t>shots_on_goal</t>
+  </si>
+  <si>
+    <t>id of the goalie who was in net and made the save on the shot</t>
+  </si>
+  <si>
+    <t>total number of shots on goal for the away team when the current shot was taken</t>
+  </si>
+  <si>
+    <t>total number of shots on goal for the home team when the current shot was taken</t>
+  </si>
+  <si>
+    <t>give_player_id</t>
+  </si>
+  <si>
+    <t>giveaways</t>
+  </si>
+  <si>
+    <t>id of the player who is charged with the giveaway</t>
+  </si>
+  <si>
+    <t>score_player_id</t>
+  </si>
+  <si>
+    <t>score_player_total</t>
+  </si>
+  <si>
+    <t>assist_1_player_id</t>
+  </si>
+  <si>
+    <t>assist_1_player_total</t>
+  </si>
+  <si>
+    <t>assist_2_player_id</t>
+  </si>
+  <si>
+    <t>assist_2_player_total</t>
+  </si>
+  <si>
+    <t>away_score</t>
+  </si>
+  <si>
+    <t>home_score</t>
+  </si>
+  <si>
+    <t>video_link</t>
+  </si>
+  <si>
+    <t>goals</t>
+  </si>
+  <si>
+    <t>id of the goalie who was in net for the goal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id of the player who scored the goal </t>
+  </si>
+  <si>
+    <t>total number of goals for the goal scorer on the season</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id of the player who has the primary assist on the goal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total number of assists on the season for the player with the primary assist </t>
+  </si>
+  <si>
+    <t xml:space="preserve">id of the player who has the secondary assist on the goal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total number of assists on the season for the player with the secondary assist </t>
+  </si>
+  <si>
+    <t>score for the away team at the time of the goal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">score for the home team at the time of the goal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">link t o video of the goal </t>
+  </si>
+  <si>
+    <t>hitter_id</t>
+  </si>
+  <si>
+    <t>hittee_id</t>
+  </si>
+  <si>
+    <t>hits</t>
+  </si>
+  <si>
+    <t>id of the player who made the hit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id of the player who was hit </t>
+  </si>
+  <si>
+    <t>take_player_id</t>
+  </si>
+  <si>
+    <t>takeaways</t>
+  </si>
+  <si>
+    <t>id of the player who was awarded with the takeaway</t>
+  </si>
+  <si>
+    <t>team_id</t>
+  </si>
+  <si>
+    <t>team</t>
+  </si>
+  <si>
+    <t>teams</t>
+  </si>
+  <si>
+    <t>numerical code indicating the team</t>
+  </si>
+  <si>
+    <t>3-letter code indicating the team name</t>
   </si>
 </sst>
 </file>
@@ -731,10 +899,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94ACE342-EFD3-426B-82E7-62E8481985EA}">
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C204"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.44140625" customWidth="1"/>
     <col min="3" max="3" width="85.21875" customWidth="1"/>
   </cols>
@@ -1443,6 +1611,1546 @@
         <v>103</v>
       </c>
     </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>2</v>
+      </c>
+      <c r="B65" t="s">
+        <v>112</v>
+      </c>
+      <c r="C65" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>112</v>
+      </c>
+      <c r="C66" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" t="s">
+        <v>112</v>
+      </c>
+      <c r="C67" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68" t="s">
+        <v>112</v>
+      </c>
+      <c r="C68" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>112</v>
+      </c>
+      <c r="C69" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>68</v>
+      </c>
+      <c r="B70" t="s">
+        <v>112</v>
+      </c>
+      <c r="C70" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>69</v>
+      </c>
+      <c r="B71" t="s">
+        <v>112</v>
+      </c>
+      <c r="C71" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>70</v>
+      </c>
+      <c r="B72" t="s">
+        <v>112</v>
+      </c>
+      <c r="C72" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>71</v>
+      </c>
+      <c r="B73" t="s">
+        <v>112</v>
+      </c>
+      <c r="C73" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>72</v>
+      </c>
+      <c r="B74" t="s">
+        <v>112</v>
+      </c>
+      <c r="C74" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>73</v>
+      </c>
+      <c r="B75" t="s">
+        <v>112</v>
+      </c>
+      <c r="C75" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>74</v>
+      </c>
+      <c r="B76" t="s">
+        <v>112</v>
+      </c>
+      <c r="C76" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>75</v>
+      </c>
+      <c r="B77" t="s">
+        <v>112</v>
+      </c>
+      <c r="C77" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>104</v>
+      </c>
+      <c r="B78" t="s">
+        <v>112</v>
+      </c>
+      <c r="C78" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>105</v>
+      </c>
+      <c r="B79" t="s">
+        <v>112</v>
+      </c>
+      <c r="C79" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>106</v>
+      </c>
+      <c r="B80" t="s">
+        <v>112</v>
+      </c>
+      <c r="C80" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>107</v>
+      </c>
+      <c r="B81" t="s">
+        <v>112</v>
+      </c>
+      <c r="C81" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>108</v>
+      </c>
+      <c r="B82" t="s">
+        <v>112</v>
+      </c>
+      <c r="C82" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>109</v>
+      </c>
+      <c r="B83" t="s">
+        <v>112</v>
+      </c>
+      <c r="C83" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>110</v>
+      </c>
+      <c r="B84" t="s">
+        <v>112</v>
+      </c>
+      <c r="C84" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>111</v>
+      </c>
+      <c r="B85" t="s">
+        <v>112</v>
+      </c>
+      <c r="C85" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>2</v>
+      </c>
+      <c r="B86" t="s">
+        <v>113</v>
+      </c>
+      <c r="C86" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>64</v>
+      </c>
+      <c r="B87" t="s">
+        <v>113</v>
+      </c>
+      <c r="C87" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>65</v>
+      </c>
+      <c r="B88" t="s">
+        <v>113</v>
+      </c>
+      <c r="C88" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>66</v>
+      </c>
+      <c r="B89" t="s">
+        <v>113</v>
+      </c>
+      <c r="C89" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>67</v>
+      </c>
+      <c r="B90" t="s">
+        <v>113</v>
+      </c>
+      <c r="C90" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>68</v>
+      </c>
+      <c r="B91" t="s">
+        <v>113</v>
+      </c>
+      <c r="C91" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>69</v>
+      </c>
+      <c r="B92" t="s">
+        <v>113</v>
+      </c>
+      <c r="C92" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>70</v>
+      </c>
+      <c r="B93" t="s">
+        <v>113</v>
+      </c>
+      <c r="C93" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>71</v>
+      </c>
+      <c r="B94" t="s">
+        <v>113</v>
+      </c>
+      <c r="C94" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>72</v>
+      </c>
+      <c r="B95" t="s">
+        <v>113</v>
+      </c>
+      <c r="C95" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>73</v>
+      </c>
+      <c r="B96" t="s">
+        <v>113</v>
+      </c>
+      <c r="C96" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>74</v>
+      </c>
+      <c r="B97" t="s">
+        <v>113</v>
+      </c>
+      <c r="C97" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>75</v>
+      </c>
+      <c r="B98" t="s">
+        <v>113</v>
+      </c>
+      <c r="C98" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" t="s">
+        <v>113</v>
+      </c>
+      <c r="C99" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>110</v>
+      </c>
+      <c r="B100" t="s">
+        <v>113</v>
+      </c>
+      <c r="C100" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>111</v>
+      </c>
+      <c r="B101" t="s">
+        <v>113</v>
+      </c>
+      <c r="C101" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>2</v>
+      </c>
+      <c r="B102" t="s">
+        <v>117</v>
+      </c>
+      <c r="C102" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>64</v>
+      </c>
+      <c r="B103" t="s">
+        <v>117</v>
+      </c>
+      <c r="C103" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>65</v>
+      </c>
+      <c r="B104" t="s">
+        <v>117</v>
+      </c>
+      <c r="C104" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>66</v>
+      </c>
+      <c r="B105" t="s">
+        <v>117</v>
+      </c>
+      <c r="C105" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>67</v>
+      </c>
+      <c r="B106" t="s">
+        <v>117</v>
+      </c>
+      <c r="C106" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>68</v>
+      </c>
+      <c r="B107" t="s">
+        <v>117</v>
+      </c>
+      <c r="C107" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>69</v>
+      </c>
+      <c r="B108" t="s">
+        <v>117</v>
+      </c>
+      <c r="C108" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>70</v>
+      </c>
+      <c r="B109" t="s">
+        <v>117</v>
+      </c>
+      <c r="C109" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>71</v>
+      </c>
+      <c r="B110" t="s">
+        <v>117</v>
+      </c>
+      <c r="C110" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>72</v>
+      </c>
+      <c r="B111" t="s">
+        <v>117</v>
+      </c>
+      <c r="C111" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>73</v>
+      </c>
+      <c r="B112" t="s">
+        <v>117</v>
+      </c>
+      <c r="C112" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>74</v>
+      </c>
+      <c r="B113" t="s">
+        <v>117</v>
+      </c>
+      <c r="C113" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>75</v>
+      </c>
+      <c r="B114" t="s">
+        <v>117</v>
+      </c>
+      <c r="C114" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>104</v>
+      </c>
+      <c r="B115" t="s">
+        <v>117</v>
+      </c>
+      <c r="C115" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>105</v>
+      </c>
+      <c r="B116" t="s">
+        <v>117</v>
+      </c>
+      <c r="C116" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>109</v>
+      </c>
+      <c r="B117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C117" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>2</v>
+      </c>
+      <c r="B118" t="s">
+        <v>120</v>
+      </c>
+      <c r="C118" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>64</v>
+      </c>
+      <c r="B119" t="s">
+        <v>120</v>
+      </c>
+      <c r="C119" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>65</v>
+      </c>
+      <c r="B120" t="s">
+        <v>120</v>
+      </c>
+      <c r="C120" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>66</v>
+      </c>
+      <c r="B121" t="s">
+        <v>120</v>
+      </c>
+      <c r="C121" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>67</v>
+      </c>
+      <c r="B122" t="s">
+        <v>120</v>
+      </c>
+      <c r="C122" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>68</v>
+      </c>
+      <c r="B123" t="s">
+        <v>120</v>
+      </c>
+      <c r="C123" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>69</v>
+      </c>
+      <c r="B124" t="s">
+        <v>120</v>
+      </c>
+      <c r="C124" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>70</v>
+      </c>
+      <c r="B125" t="s">
+        <v>120</v>
+      </c>
+      <c r="C125" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>71</v>
+      </c>
+      <c r="B126" t="s">
+        <v>120</v>
+      </c>
+      <c r="C126" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>72</v>
+      </c>
+      <c r="B127" t="s">
+        <v>120</v>
+      </c>
+      <c r="C127" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>73</v>
+      </c>
+      <c r="B128" t="s">
+        <v>120</v>
+      </c>
+      <c r="C128" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>74</v>
+      </c>
+      <c r="B129" t="s">
+        <v>120</v>
+      </c>
+      <c r="C129" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>75</v>
+      </c>
+      <c r="B130" t="s">
+        <v>120</v>
+      </c>
+      <c r="C130" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>104</v>
+      </c>
+      <c r="B131" t="s">
+        <v>120</v>
+      </c>
+      <c r="C131" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>105</v>
+      </c>
+      <c r="B132" t="s">
+        <v>120</v>
+      </c>
+      <c r="C132" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>106</v>
+      </c>
+      <c r="B133" t="s">
+        <v>120</v>
+      </c>
+      <c r="C133" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>107</v>
+      </c>
+      <c r="B134" t="s">
+        <v>120</v>
+      </c>
+      <c r="C134" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>108</v>
+      </c>
+      <c r="B135" t="s">
+        <v>120</v>
+      </c>
+      <c r="C135" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>2</v>
+      </c>
+      <c r="B136" t="s">
+        <v>125</v>
+      </c>
+      <c r="C136" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>64</v>
+      </c>
+      <c r="B137" t="s">
+        <v>125</v>
+      </c>
+      <c r="C137" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>65</v>
+      </c>
+      <c r="B138" t="s">
+        <v>125</v>
+      </c>
+      <c r="C138" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>66</v>
+      </c>
+      <c r="B139" t="s">
+        <v>125</v>
+      </c>
+      <c r="C139" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>67</v>
+      </c>
+      <c r="B140" t="s">
+        <v>125</v>
+      </c>
+      <c r="C140" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>68</v>
+      </c>
+      <c r="B141" t="s">
+        <v>125</v>
+      </c>
+      <c r="C141" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>69</v>
+      </c>
+      <c r="B142" t="s">
+        <v>125</v>
+      </c>
+      <c r="C142" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>70</v>
+      </c>
+      <c r="B143" t="s">
+        <v>125</v>
+      </c>
+      <c r="C143" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>71</v>
+      </c>
+      <c r="B144" t="s">
+        <v>125</v>
+      </c>
+      <c r="C144" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>72</v>
+      </c>
+      <c r="B145" t="s">
+        <v>125</v>
+      </c>
+      <c r="C145" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>73</v>
+      </c>
+      <c r="B146" t="s">
+        <v>125</v>
+      </c>
+      <c r="C146" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>74</v>
+      </c>
+      <c r="B147" t="s">
+        <v>125</v>
+      </c>
+      <c r="C147" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>75</v>
+      </c>
+      <c r="B148" t="s">
+        <v>125</v>
+      </c>
+      <c r="C148" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>124</v>
+      </c>
+      <c r="B149" t="s">
+        <v>125</v>
+      </c>
+      <c r="C149" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>2</v>
+      </c>
+      <c r="B150" t="s">
+        <v>136</v>
+      </c>
+      <c r="C150" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>64</v>
+      </c>
+      <c r="B151" t="s">
+        <v>136</v>
+      </c>
+      <c r="C151" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>65</v>
+      </c>
+      <c r="B152" t="s">
+        <v>136</v>
+      </c>
+      <c r="C152" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>66</v>
+      </c>
+      <c r="B153" t="s">
+        <v>136</v>
+      </c>
+      <c r="C153" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>67</v>
+      </c>
+      <c r="B154" t="s">
+        <v>136</v>
+      </c>
+      <c r="C154" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>68</v>
+      </c>
+      <c r="B155" t="s">
+        <v>136</v>
+      </c>
+      <c r="C155" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>69</v>
+      </c>
+      <c r="B156" t="s">
+        <v>136</v>
+      </c>
+      <c r="C156" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>70</v>
+      </c>
+      <c r="B157" t="s">
+        <v>136</v>
+      </c>
+      <c r="C157" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>71</v>
+      </c>
+      <c r="B158" t="s">
+        <v>136</v>
+      </c>
+      <c r="C158" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>72</v>
+      </c>
+      <c r="B159" t="s">
+        <v>136</v>
+      </c>
+      <c r="C159" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>73</v>
+      </c>
+      <c r="B160" t="s">
+        <v>136</v>
+      </c>
+      <c r="C160" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>74</v>
+      </c>
+      <c r="B161" t="s">
+        <v>136</v>
+      </c>
+      <c r="C161" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>75</v>
+      </c>
+      <c r="B162" t="s">
+        <v>136</v>
+      </c>
+      <c r="C162" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>104</v>
+      </c>
+      <c r="B163" t="s">
+        <v>136</v>
+      </c>
+      <c r="C163" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>106</v>
+      </c>
+      <c r="B164" t="s">
+        <v>136</v>
+      </c>
+      <c r="C164" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>127</v>
+      </c>
+      <c r="B165" t="s">
+        <v>136</v>
+      </c>
+      <c r="C165" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>128</v>
+      </c>
+      <c r="B166" t="s">
+        <v>136</v>
+      </c>
+      <c r="C166" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>129</v>
+      </c>
+      <c r="B167" t="s">
+        <v>136</v>
+      </c>
+      <c r="C167" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>130</v>
+      </c>
+      <c r="B168" t="s">
+        <v>136</v>
+      </c>
+      <c r="C168" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>131</v>
+      </c>
+      <c r="B169" t="s">
+        <v>136</v>
+      </c>
+      <c r="C169" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>132</v>
+      </c>
+      <c r="B170" t="s">
+        <v>136</v>
+      </c>
+      <c r="C170" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>133</v>
+      </c>
+      <c r="B171" t="s">
+        <v>136</v>
+      </c>
+      <c r="C171" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>134</v>
+      </c>
+      <c r="B172" t="s">
+        <v>136</v>
+      </c>
+      <c r="C172" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>135</v>
+      </c>
+      <c r="B173" t="s">
+        <v>136</v>
+      </c>
+      <c r="C173" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>2</v>
+      </c>
+      <c r="B174" t="s">
+        <v>149</v>
+      </c>
+      <c r="C174" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>64</v>
+      </c>
+      <c r="B175" t="s">
+        <v>149</v>
+      </c>
+      <c r="C175" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>65</v>
+      </c>
+      <c r="B176" t="s">
+        <v>149</v>
+      </c>
+      <c r="C176" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>66</v>
+      </c>
+      <c r="B177" t="s">
+        <v>149</v>
+      </c>
+      <c r="C177" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>67</v>
+      </c>
+      <c r="B178" t="s">
+        <v>149</v>
+      </c>
+      <c r="C178" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>68</v>
+      </c>
+      <c r="B179" t="s">
+        <v>149</v>
+      </c>
+      <c r="C179" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>69</v>
+      </c>
+      <c r="B180" t="s">
+        <v>149</v>
+      </c>
+      <c r="C180" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>70</v>
+      </c>
+      <c r="B181" t="s">
+        <v>149</v>
+      </c>
+      <c r="C181" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>71</v>
+      </c>
+      <c r="B182" t="s">
+        <v>149</v>
+      </c>
+      <c r="C182" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>72</v>
+      </c>
+      <c r="B183" t="s">
+        <v>149</v>
+      </c>
+      <c r="C183" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>73</v>
+      </c>
+      <c r="B184" t="s">
+        <v>149</v>
+      </c>
+      <c r="C184" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>74</v>
+      </c>
+      <c r="B185" t="s">
+        <v>149</v>
+      </c>
+      <c r="C185" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>75</v>
+      </c>
+      <c r="B186" t="s">
+        <v>149</v>
+      </c>
+      <c r="C186" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>147</v>
+      </c>
+      <c r="B187" t="s">
+        <v>149</v>
+      </c>
+      <c r="C187" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>148</v>
+      </c>
+      <c r="B188" t="s">
+        <v>149</v>
+      </c>
+      <c r="C188" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>2</v>
+      </c>
+      <c r="B189" t="s">
+        <v>153</v>
+      </c>
+      <c r="C189" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>64</v>
+      </c>
+      <c r="B190" t="s">
+        <v>153</v>
+      </c>
+      <c r="C190" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>65</v>
+      </c>
+      <c r="B191" t="s">
+        <v>153</v>
+      </c>
+      <c r="C191" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>66</v>
+      </c>
+      <c r="B192" t="s">
+        <v>153</v>
+      </c>
+      <c r="C192" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>67</v>
+      </c>
+      <c r="B193" t="s">
+        <v>153</v>
+      </c>
+      <c r="C193" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>68</v>
+      </c>
+      <c r="B194" t="s">
+        <v>153</v>
+      </c>
+      <c r="C194" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>69</v>
+      </c>
+      <c r="B195" t="s">
+        <v>153</v>
+      </c>
+      <c r="C195" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>70</v>
+      </c>
+      <c r="B196" t="s">
+        <v>153</v>
+      </c>
+      <c r="C196" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>71</v>
+      </c>
+      <c r="B197" t="s">
+        <v>153</v>
+      </c>
+      <c r="C197" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>72</v>
+      </c>
+      <c r="B198" t="s">
+        <v>153</v>
+      </c>
+      <c r="C198" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>73</v>
+      </c>
+      <c r="B199" t="s">
+        <v>153</v>
+      </c>
+      <c r="C199" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>74</v>
+      </c>
+      <c r="B200" t="s">
+        <v>153</v>
+      </c>
+      <c r="C200" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>75</v>
+      </c>
+      <c r="B201" t="s">
+        <v>153</v>
+      </c>
+      <c r="C201" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>152</v>
+      </c>
+      <c r="B202" t="s">
+        <v>153</v>
+      </c>
+      <c r="C202" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>155</v>
+      </c>
+      <c r="B203" t="s">
+        <v>157</v>
+      </c>
+      <c r="C203" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>156</v>
+      </c>
+      <c r="B204" t="s">
+        <v>157</v>
+      </c>
+      <c r="C204" t="s">
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025-2026/Data/Data_Dictionary.xlsx
+++ b/2025-2026/Data/Data_Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\Documents\NHL-Stats\2025-2026\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3554E4-538B-4B9E-A20C-3D2040C64C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C444ED7-63A7-4DE7-9271-2F06CCBC312C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{63DB0C7C-412E-4A18-A7BF-880A50C6E4C7}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{63DB0C7C-412E-4A18-A7BF-880A50C6E4C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="286">
   <si>
     <t>Variable</t>
   </si>
@@ -519,6 +519,384 @@
   </si>
   <si>
     <t>3-letter code indicating the team name</t>
+  </si>
+  <si>
+    <t>player_id</t>
+  </si>
+  <si>
+    <t>games_played</t>
+  </si>
+  <si>
+    <t>games_started</t>
+  </si>
+  <si>
+    <t>wins</t>
+  </si>
+  <si>
+    <t>losses</t>
+  </si>
+  <si>
+    <t>ot_losses</t>
+  </si>
+  <si>
+    <t>assist</t>
+  </si>
+  <si>
+    <t>goals_against</t>
+  </si>
+  <si>
+    <t>gaa</t>
+  </si>
+  <si>
+    <t>pim</t>
+  </si>
+  <si>
+    <t>save_pctg</t>
+  </si>
+  <si>
+    <t>shots_against</t>
+  </si>
+  <si>
+    <t>shutouts</t>
+  </si>
+  <si>
+    <t>goalie_career_reg_stats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">numerical id of the player </t>
+  </si>
+  <si>
+    <t>total number of games played in the goalie's career</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total number of wins credited to the goalie in their career </t>
+  </si>
+  <si>
+    <t>total number of games the goalie started in their career</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total number of losses credited to the goalie in their career </t>
+  </si>
+  <si>
+    <t>total number of ot_losses credited to the goalie in their career</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total number of goals scored by the goalie in their career </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total number of assists in the goalie's career </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total number of goals allowed against by the goalie in their career </t>
+  </si>
+  <si>
+    <t xml:space="preserve">goalie's career goals against average </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total penalty minutes taken in the goalie's career </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total save percentage across the goalie's career </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total number of shots the goalie faced in their career </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total number of shutouts the goalie had in their career </t>
+  </si>
+  <si>
+    <t>shut_outs</t>
+  </si>
+  <si>
+    <t>goalie_reg_stats</t>
+  </si>
+  <si>
+    <t>total number of games played in the 2025-2026 regular season</t>
+  </si>
+  <si>
+    <t>total number of wins credited to the goalie in the 2025-2026 regular season</t>
+  </si>
+  <si>
+    <t>total number of losses credited to the goalie in the 2025-2026 regular season</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total number of ot losses credited to the goalie in the 2025-2026 regular season </t>
+  </si>
+  <si>
+    <t xml:space="preserve">the 2025-2026 regular season goals against average </t>
+  </si>
+  <si>
+    <t>2025-2026 regular season save percentage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total number of shut outs in the 2025-2026 regular season </t>
+  </si>
+  <si>
+    <t>first_name</t>
+  </si>
+  <si>
+    <t>last_name</t>
+  </si>
+  <si>
+    <t>birth_date</t>
+  </si>
+  <si>
+    <t>is_active</t>
+  </si>
+  <si>
+    <t>current_team_id</t>
+  </si>
+  <si>
+    <t>position</t>
+  </si>
+  <si>
+    <t>shoots_catches</t>
+  </si>
+  <si>
+    <t>height_inches</t>
+  </si>
+  <si>
+    <t>height_cm</t>
+  </si>
+  <si>
+    <t>weight_lbs</t>
+  </si>
+  <si>
+    <t>weight_kg</t>
+  </si>
+  <si>
+    <t>birth_city</t>
+  </si>
+  <si>
+    <t>birth_state_prov</t>
+  </si>
+  <si>
+    <t>birth_country</t>
+  </si>
+  <si>
+    <t>draft_year</t>
+  </si>
+  <si>
+    <t>draft_team</t>
+  </si>
+  <si>
+    <t>draft_round</t>
+  </si>
+  <si>
+    <t>draft_pick_in_round</t>
+  </si>
+  <si>
+    <t>draft_overall_pick</t>
+  </si>
+  <si>
+    <t>head_shot</t>
+  </si>
+  <si>
+    <t>hero_image</t>
+  </si>
+  <si>
+    <t>player_info</t>
+  </si>
+  <si>
+    <t>first name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">last name </t>
+  </si>
+  <si>
+    <t xml:space="preserve">date of birth </t>
+  </si>
+  <si>
+    <t>indicates whether the player is active or not: TRUE, FALSE - as of Apr 30 2026</t>
+  </si>
+  <si>
+    <t>the numerical id of the player's current team - as of Apr 30, 2026</t>
+  </si>
+  <si>
+    <t>player position: C, D, G, L, R</t>
+  </si>
+  <si>
+    <t>the way the player shoots or catches: L, R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">height in centimetre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">height in inches </t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight in pounds </t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight in kilograms </t>
+  </si>
+  <si>
+    <t xml:space="preserve">city of birth </t>
+  </si>
+  <si>
+    <t>state or province of birth - only for Canadians and Americans</t>
+  </si>
+  <si>
+    <t>country of birth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">draft year </t>
+  </si>
+  <si>
+    <t>team player was drafted by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">round player was drafted in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">pick number of the round the player was drafted </t>
+  </si>
+  <si>
+    <t xml:space="preserve">overall draft pick number </t>
+  </si>
+  <si>
+    <t>link to an image of a headshot</t>
+  </si>
+  <si>
+    <t>link to an image of an action shot</t>
+  </si>
+  <si>
+    <t>avg_toi</t>
+  </si>
+  <si>
+    <t>assists</t>
+  </si>
+  <si>
+    <t>points</t>
+  </si>
+  <si>
+    <t>gwg</t>
+  </si>
+  <si>
+    <t>ot_goals</t>
+  </si>
+  <si>
+    <t>shots</t>
+  </si>
+  <si>
+    <t>fo_win_pctg</t>
+  </si>
+  <si>
+    <t>plus_minus</t>
+  </si>
+  <si>
+    <t>shooting_pctg</t>
+  </si>
+  <si>
+    <t>pp_goals</t>
+  </si>
+  <si>
+    <t>pp_points</t>
+  </si>
+  <si>
+    <t>sh_goals</t>
+  </si>
+  <si>
+    <t>sh_points</t>
+  </si>
+  <si>
+    <t>skater_career_reg_stats</t>
+  </si>
+  <si>
+    <t>skater_reg_stats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total career regular season goals </t>
+  </si>
+  <si>
+    <t xml:space="preserve">average time on ice in the regular season throughout their career </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total regular season games played </t>
+  </si>
+  <si>
+    <t xml:space="preserve">totalcareer regular season  faceoff win percentage </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total career regular season  shots </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total career regular season  overtime goals </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total career regular season  game winning goals </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total career regular season  points </t>
+  </si>
+  <si>
+    <t>total career regular season  assists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total career regular season penalty minutes </t>
+  </si>
+  <si>
+    <t>total career regular season plus/minus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total career regular season shooting percentage </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total career regular season  power play goals </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total career regular season power play points </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total career regular season short handed goals </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total careet regular season short handed points </t>
+  </si>
+  <si>
+    <t xml:space="preserve">numerical player id </t>
+  </si>
+  <si>
+    <t>total games played in the 2025-2026 regular season</t>
+  </si>
+  <si>
+    <t>total goals scored in the 2025-2026 regular season</t>
+  </si>
+  <si>
+    <t>total assists in the 2025-2026 regular season</t>
+  </si>
+  <si>
+    <t>total points in the 2025-2026 regular season</t>
+  </si>
+  <si>
+    <t>total game winning goals in the 2025-2026 regular season</t>
+  </si>
+  <si>
+    <t>total overtime goals scored in the 2025-2026 regular season</t>
+  </si>
+  <si>
+    <t>total shots on goal in the 2025-2026 regular season</t>
+  </si>
+  <si>
+    <t>shooting percentage in the 2025-2026 regular season</t>
+  </si>
+  <si>
+    <t>total penalty minutes in the 2025-2026 regular season</t>
+  </si>
+  <si>
+    <t>total plus/minus for the 2025-2026 regular season</t>
+  </si>
+  <si>
+    <t>total power play goals scored in the 2025-2026 regular season</t>
+  </si>
+  <si>
+    <t>total power play points in the 2025-2026 regular season</t>
+  </si>
+  <si>
+    <t>total short handed goals scored in the 2025-2026 regular season</t>
+  </si>
+  <si>
+    <t>total short handed points in the 2025-2026 regular season</t>
   </si>
 </sst>
 </file>
@@ -899,11 +1277,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94ACE342-EFD3-426B-82E7-62E8481985EA}">
-  <dimension ref="A1:C204"/>
+  <dimension ref="A1:C280"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="85.21875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3151,6 +3529,842 @@
         <v>159</v>
       </c>
     </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>160</v>
+      </c>
+      <c r="B205" t="s">
+        <v>173</v>
+      </c>
+      <c r="C205" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>161</v>
+      </c>
+      <c r="B206" t="s">
+        <v>173</v>
+      </c>
+      <c r="C206" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>162</v>
+      </c>
+      <c r="B207" t="s">
+        <v>173</v>
+      </c>
+      <c r="C207" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>163</v>
+      </c>
+      <c r="B208" t="s">
+        <v>173</v>
+      </c>
+      <c r="C208" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>164</v>
+      </c>
+      <c r="B209" t="s">
+        <v>173</v>
+      </c>
+      <c r="C209" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>165</v>
+      </c>
+      <c r="B210" t="s">
+        <v>173</v>
+      </c>
+      <c r="C210" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>136</v>
+      </c>
+      <c r="B211" t="s">
+        <v>173</v>
+      </c>
+      <c r="C211" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>166</v>
+      </c>
+      <c r="B212" t="s">
+        <v>173</v>
+      </c>
+      <c r="C212" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>167</v>
+      </c>
+      <c r="B213" t="s">
+        <v>173</v>
+      </c>
+      <c r="C213" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>168</v>
+      </c>
+      <c r="B214" t="s">
+        <v>173</v>
+      </c>
+      <c r="C214" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>169</v>
+      </c>
+      <c r="B215" t="s">
+        <v>173</v>
+      </c>
+      <c r="C215" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>170</v>
+      </c>
+      <c r="B216" t="s">
+        <v>173</v>
+      </c>
+      <c r="C216" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>171</v>
+      </c>
+      <c r="B217" t="s">
+        <v>173</v>
+      </c>
+      <c r="C217" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>172</v>
+      </c>
+      <c r="B218" t="s">
+        <v>173</v>
+      </c>
+      <c r="C218" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>160</v>
+      </c>
+      <c r="B219" t="s">
+        <v>189</v>
+      </c>
+      <c r="C219" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>161</v>
+      </c>
+      <c r="B220" t="s">
+        <v>189</v>
+      </c>
+      <c r="C220" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>163</v>
+      </c>
+      <c r="B221" t="s">
+        <v>189</v>
+      </c>
+      <c r="C221" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>164</v>
+      </c>
+      <c r="B222" t="s">
+        <v>189</v>
+      </c>
+      <c r="C222" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>165</v>
+      </c>
+      <c r="B223" t="s">
+        <v>189</v>
+      </c>
+      <c r="C223" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>168</v>
+      </c>
+      <c r="B224" t="s">
+        <v>189</v>
+      </c>
+      <c r="C224" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>170</v>
+      </c>
+      <c r="B225" t="s">
+        <v>189</v>
+      </c>
+      <c r="C225" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>188</v>
+      </c>
+      <c r="B226" t="s">
+        <v>189</v>
+      </c>
+      <c r="C226" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>160</v>
+      </c>
+      <c r="B227" t="s">
+        <v>218</v>
+      </c>
+      <c r="C227" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>197</v>
+      </c>
+      <c r="B228" t="s">
+        <v>218</v>
+      </c>
+      <c r="C228" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>198</v>
+      </c>
+      <c r="B229" t="s">
+        <v>218</v>
+      </c>
+      <c r="C229" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>199</v>
+      </c>
+      <c r="B230" t="s">
+        <v>218</v>
+      </c>
+      <c r="C230" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>200</v>
+      </c>
+      <c r="B231" t="s">
+        <v>218</v>
+      </c>
+      <c r="C231" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>201</v>
+      </c>
+      <c r="B232" t="s">
+        <v>218</v>
+      </c>
+      <c r="C232" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>202</v>
+      </c>
+      <c r="B233" t="s">
+        <v>218</v>
+      </c>
+      <c r="C233" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>203</v>
+      </c>
+      <c r="B234" t="s">
+        <v>218</v>
+      </c>
+      <c r="C234" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>204</v>
+      </c>
+      <c r="B235" t="s">
+        <v>218</v>
+      </c>
+      <c r="C235" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>205</v>
+      </c>
+      <c r="B236" t="s">
+        <v>218</v>
+      </c>
+      <c r="C236" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>206</v>
+      </c>
+      <c r="B237" t="s">
+        <v>218</v>
+      </c>
+      <c r="C237" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>207</v>
+      </c>
+      <c r="B238" t="s">
+        <v>218</v>
+      </c>
+      <c r="C238" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>208</v>
+      </c>
+      <c r="B239" t="s">
+        <v>218</v>
+      </c>
+      <c r="C239" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>209</v>
+      </c>
+      <c r="B240" t="s">
+        <v>218</v>
+      </c>
+      <c r="C240" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>210</v>
+      </c>
+      <c r="B241" t="s">
+        <v>218</v>
+      </c>
+      <c r="C241" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>211</v>
+      </c>
+      <c r="B242" t="s">
+        <v>218</v>
+      </c>
+      <c r="C242" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>212</v>
+      </c>
+      <c r="B243" t="s">
+        <v>218</v>
+      </c>
+      <c r="C243" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>213</v>
+      </c>
+      <c r="B244" t="s">
+        <v>218</v>
+      </c>
+      <c r="C244" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>214</v>
+      </c>
+      <c r="B245" t="s">
+        <v>218</v>
+      </c>
+      <c r="C245" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>215</v>
+      </c>
+      <c r="B246" t="s">
+        <v>218</v>
+      </c>
+      <c r="C246" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>216</v>
+      </c>
+      <c r="B247" t="s">
+        <v>218</v>
+      </c>
+      <c r="C247" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>217</v>
+      </c>
+      <c r="B248" t="s">
+        <v>218</v>
+      </c>
+      <c r="C248" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>160</v>
+      </c>
+      <c r="B249" t="s">
+        <v>253</v>
+      </c>
+      <c r="C249" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>161</v>
+      </c>
+      <c r="B250" t="s">
+        <v>253</v>
+      </c>
+      <c r="C250" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>240</v>
+      </c>
+      <c r="B251" t="s">
+        <v>253</v>
+      </c>
+      <c r="C251" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>136</v>
+      </c>
+      <c r="B252" t="s">
+        <v>253</v>
+      </c>
+      <c r="C252" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>241</v>
+      </c>
+      <c r="B253" t="s">
+        <v>253</v>
+      </c>
+      <c r="C253" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>242</v>
+      </c>
+      <c r="B254" t="s">
+        <v>253</v>
+      </c>
+      <c r="C254" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>243</v>
+      </c>
+      <c r="B255" t="s">
+        <v>253</v>
+      </c>
+      <c r="C255" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>244</v>
+      </c>
+      <c r="B256" t="s">
+        <v>253</v>
+      </c>
+      <c r="C256" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>245</v>
+      </c>
+      <c r="B257" t="s">
+        <v>253</v>
+      </c>
+      <c r="C257" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>246</v>
+      </c>
+      <c r="B258" t="s">
+        <v>253</v>
+      </c>
+      <c r="C258" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>169</v>
+      </c>
+      <c r="B259" t="s">
+        <v>253</v>
+      </c>
+      <c r="C259" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>247</v>
+      </c>
+      <c r="B260" t="s">
+        <v>253</v>
+      </c>
+      <c r="C260" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>248</v>
+      </c>
+      <c r="B261" t="s">
+        <v>253</v>
+      </c>
+      <c r="C261" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>249</v>
+      </c>
+      <c r="B262" t="s">
+        <v>253</v>
+      </c>
+      <c r="C262" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>250</v>
+      </c>
+      <c r="B263" t="s">
+        <v>253</v>
+      </c>
+      <c r="C263" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>251</v>
+      </c>
+      <c r="B264" t="s">
+        <v>253</v>
+      </c>
+      <c r="C264" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>252</v>
+      </c>
+      <c r="B265" t="s">
+        <v>253</v>
+      </c>
+      <c r="C265" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>160</v>
+      </c>
+      <c r="B266" t="s">
+        <v>254</v>
+      </c>
+      <c r="C266" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>161</v>
+      </c>
+      <c r="B267" t="s">
+        <v>254</v>
+      </c>
+      <c r="C267" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>136</v>
+      </c>
+      <c r="B268" t="s">
+        <v>254</v>
+      </c>
+      <c r="C268" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>241</v>
+      </c>
+      <c r="B269" t="s">
+        <v>254</v>
+      </c>
+      <c r="C269" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>242</v>
+      </c>
+      <c r="B270" t="s">
+        <v>254</v>
+      </c>
+      <c r="C270" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>243</v>
+      </c>
+      <c r="B271" t="s">
+        <v>254</v>
+      </c>
+      <c r="C271" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>244</v>
+      </c>
+      <c r="B272" t="s">
+        <v>254</v>
+      </c>
+      <c r="C272" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>245</v>
+      </c>
+      <c r="B273" t="s">
+        <v>254</v>
+      </c>
+      <c r="C273" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>248</v>
+      </c>
+      <c r="B274" t="s">
+        <v>254</v>
+      </c>
+      <c r="C274" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>169</v>
+      </c>
+      <c r="B275" t="s">
+        <v>254</v>
+      </c>
+      <c r="C275" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>247</v>
+      </c>
+      <c r="B276" t="s">
+        <v>254</v>
+      </c>
+      <c r="C276" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>249</v>
+      </c>
+      <c r="B277" t="s">
+        <v>254</v>
+      </c>
+      <c r="C277" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>250</v>
+      </c>
+      <c r="B278" t="s">
+        <v>254</v>
+      </c>
+      <c r="C278" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>251</v>
+      </c>
+      <c r="B279" t="s">
+        <v>254</v>
+      </c>
+      <c r="C279" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>252</v>
+      </c>
+      <c r="B280" t="s">
+        <v>254</v>
+      </c>
+      <c r="C280" t="s">
+        <v>285</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
